--- a/投稿予約表.xlsx
+++ b/投稿予約表.xlsx
@@ -32,36 +32,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <sz val="12"/>
     </font>
   </fonts>
